--- a/data/trans_dic/IP1013-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1013-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen sordera o problemas de audición</t>
+          <t>Menores que padecen sordera o problemas de audición (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
     </row>
@@ -787,37 +788,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,81</t>
+          <t>0,09; 0,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,87</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,38</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,59</t>
+          <t>0,09; 0,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen sordera o problemas de audición (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3134</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3935</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3452</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3150</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4655</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3922</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3842</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3411</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3817</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4993</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4761</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4841</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3137</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5163</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4319</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4055</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4428</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>659; 5800</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5306</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3376</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>625; 5655</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>621; 5737</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1364; 8305</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>597; 5732</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1013-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1013-Habitat-trans_dic.xlsx
@@ -683,22 +683,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,08; 0,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,76</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,57</t>
+          <t>0,14; 0,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,4</t>
+          <t>0,04; 0,39</t>
         </is>
       </c>
     </row>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3134</t>
+          <t>0; 3813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3935</t>
+          <t>0; 5239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3150</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4655</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3884</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 4401</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3411</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3817</t>
+          <t>0; 3330</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 4408</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4761</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 4422</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4841</t>
+          <t>0; 4602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3137</t>
+          <t>0; 3666</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5163</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4319</t>
+          <t>0; 4229</t>
         </is>
       </c>
     </row>
@@ -2069,27 +2069,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4428</t>
+          <t>0; 3822</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>659; 5800</t>
+          <t>656; 5789</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5306</t>
+          <t>597; 5993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>625; 5655</t>
+          <t>624; 5307</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>621; 5737</t>
+          <t>621; 5205</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1364; 8305</t>
+          <t>1977; 8782</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>597; 5732</t>
+          <t>597; 5655</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1013-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1013-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,82</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,09; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,08; 0,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,37</t>
+          <t>0,04; 0,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,6</t>
+          <t>0,09; 0,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,39</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1321,22 +1321,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>771</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4269</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3813</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5239</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4101</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3618</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3205</t>
+          <t>0; 3705</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 4134</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3884</t>
+          <t>0; 4277</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1474,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1527,27 +1527,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>685</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4401</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3410</t>
+          <t>0; 3367</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3330</t>
+          <t>0; 3445</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4408</t>
+          <t>0; 4446</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1858,27 +1858,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1302</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 2823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4602</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3666</t>
+          <t>0; 4122</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4733</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4915</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4503</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2074</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3822</t>
+          <t>0; 3375</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>656; 5789</t>
+          <t>623; 5301</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>597; 5993</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 4443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>624; 5307</t>
+          <t>660; 5725</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>597; 6099</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>621; 5205</t>
+          <t>625; 5388</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1977; 8782</t>
+          <t>1354; 8572</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>597; 5655</t>
+          <t>596; 5875</t>
         </is>
       </c>
     </row>
